--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/oct-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2059,7 +2059,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057492-3748-CM26</t>
+          <t>3178-3106-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2084,41 +2084,37 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.102.025-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5642.29</v>
+        <v>4185.93</v>
       </c>
     </row>
     <row r="28">
@@ -2189,7 +2185,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3178-3106-CM26</t>
+          <t>1057492-3748-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2214,37 +2210,41 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.102.025-2</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4185.93</v>
+        <v>5642.29</v>
       </c>
     </row>
     <row r="30">
@@ -2372,7 +2372,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>699866-9755-CM26</t>
+          <t>4502-936-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2392,17 +2392,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3903.42</v>
+        <v>4488.94</v>
       </c>
     </row>
     <row r="33">
@@ -2502,7 +2502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4502-936-CM26</t>
+          <t>699866-9755-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4488.94</v>
+        <v>3903.42</v>
       </c>
     </row>
     <row r="35">
@@ -2872,7 +2872,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3378-8713-CM26</t>
+          <t>3378-8712-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3378-8712-CM26</t>
+          <t>3378-8711-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3851.69</v>
+        <v>2542.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3378-8711-CM26</t>
+          <t>4502-939-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3014,48 +3014,52 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2542.83</v>
+        <v>45000.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4502-939-CM26</t>
+          <t>4502-938-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3095,12 +3099,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3114,13 +3118,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>45000.95</v>
+        <v>4467.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4502-938-CM26</t>
+          <t>1057417-16829-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3145,27 +3149,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3179,13 +3183,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4467.12</v>
+        <v>64527.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057417-16829-CM26</t>
+          <t>3378-8713-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3205,52 +3209,48 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>64527.95</v>
+        <v>3851.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057439-6644-CM26</t>
+          <t>2258-7911-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3275,17 +3275,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3309,13 +3309,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7952.33</v>
+        <v>2544.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2258-7911-CM26</t>
+          <t>2258-7631-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3355,32 +3355,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2544.74</v>
+        <v>14857.81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2258-7631-CM26</t>
+          <t>2258-7617-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3435,13 +3431,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>14857.81</v>
+        <v>3657.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2258-7617-CM26</t>
+          <t>2258-7501-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3496,13 +3492,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3657.63</v>
+        <v>8641.85</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2258-7501-CM26</t>
+          <t>1057439-6644-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3522,42 +3518,46 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>8641.85</v>
+        <v>7952.33</v>
       </c>
     </row>
     <row r="51">
@@ -3937,7 +3937,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3178-3061-CM26</t>
+          <t>898-3528-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3962,27 +3962,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.102.025-2</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3992,13 +3992,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>11699.83</v>
+        <v>5332.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2258-8238-CM26</t>
+          <t>3178-3061-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4023,27 +4023,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.102.025-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>20409.08</v>
+        <v>11699.83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057049-18978-CM26</t>
+          <t>2258-8238-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4084,27 +4084,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>11552.69</v>
+        <v>20409.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5083-532-CM26</t>
+          <t>1057049-18978-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4145,27 +4145,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3223.88</v>
+        <v>11552.69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-10618-CM26</t>
+          <t>5083-532-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4206,47 +4206,43 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5715.37</v>
+        <v>3223.88</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057539-8282-CM26</t>
+          <t>1704-5886-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4271,27 +4267,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4301,13 +4297,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>57980.76</v>
+        <v>6215.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057402-11095-CM26</t>
+          <t>4502-944-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4332,27 +4328,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4366,13 +4362,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6113.73</v>
+        <v>2872.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057501-12037-CM26</t>
+          <t>5083-531-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4397,47 +4393,43 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2518.1</v>
+        <v>18306.91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5083-531-CM26</t>
+          <t>1422830-191-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4462,27 +4454,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4492,13 +4484,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>18306.91</v>
+        <v>66826.35000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1704-5886-CM26</t>
+          <t>1057402-11095-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4523,43 +4515,47 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6215.59</v>
+        <v>6113.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4502-944-CM26</t>
+          <t>1057539-8282-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4584,47 +4580,43 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2872.04</v>
+        <v>57980.76</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1422830-191-CM26</t>
+          <t>1057402-10618-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4649,101 +4641,170 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>66826.35000000001</v>
+        <v>5715.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>1057501-12037-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>2518.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>1704-5917-CM26</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>61.606.608-0</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>TRIMED CHILE SPA</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n">
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
         <v>25121.26</v>
       </c>
     </row>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/oct-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>699866-9755-CM26</t>
+          <t>1171142-3628-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2522,52 +2522,48 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>62.000.830-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3903.42</v>
+        <v>3494.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1171142-3628-CM26</t>
+          <t>699866-9755-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2587,48 +2583,52 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.830-3</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3494.7</v>
+        <v>3903.42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057417-16269-CM26</t>
+          <t>1057417-16268-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12602.06</v>
+        <v>39264.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057417-16268-CM26</t>
+          <t>1057417-16266-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2744,13 +2744,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>39264.2</v>
+        <v>20205.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057417-16267-CM26</t>
+          <t>1057417-16269-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>21599.84</v>
+        <v>12602.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057417-16266-CM26</t>
+          <t>1057417-16267-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>20205.85</v>
+        <v>21599.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3378-8712-CM26</t>
+          <t>2258-7501-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3851.69</v>
+        <v>8641.85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3378-8711-CM26</t>
+          <t>2258-7617-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2542.83</v>
+        <v>3657.63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4502-939-CM26</t>
+          <t>2258-7631-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3014,52 +3014,48 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>45000.95</v>
+        <v>14857.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4502-938-CM26</t>
+          <t>2258-7911-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3084,27 +3080,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3118,7 +3114,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4467.12</v>
+        <v>2544.74</v>
       </c>
     </row>
     <row r="44">
@@ -3189,7 +3185,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3378-8713-CM26</t>
+          <t>4502-938-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3209,48 +3205,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3851.69</v>
+        <v>4467.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2258-7911-CM26</t>
+          <t>4502-939-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3275,27 +3275,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3309,13 +3309,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2544.74</v>
+        <v>45000.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2258-7631-CM26</t>
+          <t>3378-8711-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>14857.81</v>
+        <v>2542.83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2258-7617-CM26</t>
+          <t>3378-8712-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3431,13 +3431,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3657.63</v>
+        <v>3851.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2258-7501-CM26</t>
+          <t>3378-8713-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8641.85</v>
+        <v>3851.69</v>
       </c>
     </row>
     <row r="50">
@@ -3624,7 +3624,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1422830-185-CM26</t>
+          <t>5083-524-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3649,47 +3649,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4044.66</v>
+        <v>6070.98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5083-524-CM26</t>
+          <t>1422830-185-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3714,43 +3710,47 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6070.98</v>
+        <v>4044.66</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2111-13124-CM26</t>
+          <t>898-3528-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3770,32 +3770,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2276.71</v>
+        <v>5332.74</v>
       </c>
     </row>
     <row r="55">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>898-3528-CM26</t>
+          <t>2111-13124-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3957,32 +3957,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5332.74</v>
+        <v>2276.71</v>
       </c>
     </row>
     <row r="58">
@@ -4242,7 +4242,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1704-5886-CM26</t>
+          <t>1422830-191-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6215.59</v>
+        <v>66826.35000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4502-944-CM26</t>
+          <t>1555-3000-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4328,47 +4328,43 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2872.04</v>
+        <v>13564.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5083-531-CM26</t>
+          <t>4502-944-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4393,12 +4389,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4408,28 +4404,32 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>18306.91</v>
+        <v>2872.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1422830-191-CM26</t>
+          <t>1704-5886-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>66826.35000000001</v>
+        <v>6215.59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057402-11095-CM26</t>
+          <t>5083-531-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4515,41 +4515,37 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6113.73</v>
+        <v>18306.91</v>
       </c>
     </row>
     <row r="67">
@@ -4616,7 +4612,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1057402-10618-CM26</t>
+          <t>1057402-11095-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4636,7 +4632,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4675,13 +4671,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5715.37</v>
+        <v>6113.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1057501-12037-CM26</t>
+          <t>1057402-10659-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4706,106 +4702,293 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2518.1</v>
+        <v>4280.73</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>1057402-10618-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>5715.37</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1057501-12037-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>2518.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>1704-5917-CM26</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>61.606.608-0</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>TRIMED CHILE SPA</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="n">
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
         <v>25121.26</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3391-586-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>4513.02</v>
       </c>
     </row>
   </sheetData>
